--- a/Configs/GameConfig/Datas/fg/#BuildingTier-建筑等级.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingTier-建筑等级.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,11 @@
           <t>valueKey</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>powerDemand</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -519,6 +524,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -569,6 +579,11 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>效果的说明文本键,{0}=效果值</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>FG4-ECO-11:这一级的耗电(0=按 fg.TbBuilding.powerDemand;超控阵列 80/120/160)</t>
         </is>
       </c>
     </row>
@@ -611,6 +626,9 @@
           <t>building.tier.value.warehouse</t>
         </is>
       </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -651,6 +669,9 @@
           <t>building.tier.value.warehouse</t>
         </is>
       </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -691,6 +712,9 @@
           <t>building.tier.value.warehouse</t>
         </is>
       </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -731,6 +755,9 @@
           <t>building.tier.value.signal_tower</t>
         </is>
       </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -770,6 +797,138 @@
         <is>
           <t>building.tier.value.signal_tower</t>
         </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>override_array.t1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>override_array</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>research:signal.override_t1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>research.hint.override_t1</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>building.tier.value.override_array</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>override_array.t2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>override_array</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>80</v>
+      </c>
+      <c r="F10" t="n">
+        <v>45</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>research:signal.override_t2</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>research.hint.override_t2</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>building.tier.value.override_array</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>override_array.t3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>override_array</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>120</v>
+      </c>
+      <c r="F11" t="n">
+        <v>60</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>research:signal.override_t3</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>research.hint.override_t3</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>building.tier.value.override_array</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#BuildingTier-建筑等级.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingTier-建筑等级.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -653,12 +653,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>research:logistics.warehouse_t2</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>grid.unlock.always</t>
+          <t>research.hint.logistics.warehouse_t2</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -696,12 +696,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>research:logistics.warehouse_t3</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>grid.unlock.always</t>
+          <t>research.hint.logistics.warehouse_t3</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -782,12 +782,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>research:signal.tower_t2</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>grid.unlock.always</t>
+          <t>research.hint.signal.tower_t2</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -830,7 +830,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>research.hint.override_t1</t>
+          <t>research.hint.signal.override_t1</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -873,7 +873,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>research.hint.override_t2</t>
+          <t>research.hint.signal.override_t2</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>research.hint.override_t3</t>
+          <t>research.hint.signal.override_t3</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -929,6 +929,135 @@
       </c>
       <c r="K11" t="n">
         <v>160</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>sim_lab.t1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>sim_lab</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>building.tier.value.sim_lab</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>sim_lab.t2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>sim_lab</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>60</v>
+      </c>
+      <c r="F13" t="n">
+        <v>30</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>research:industry.lab_t2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>research.hint.industry.lab_t2</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>building.tier.value.sim_lab</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>sim_lab.t3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>sim_lab</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>90</v>
+      </c>
+      <c r="F14" t="n">
+        <v>40</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>research:industry.lab_t3</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>research.hint.industry.lab_t3</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>building.tier.value.sim_lab</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#BuildingTier-建筑等级.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingTier-建筑等级.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1060,6 +1060,264 @@
         <v>30</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>turret_light.t1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>turret_light</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>building.tier.value.turret</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>turret_light.t2</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>turret_light</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>40</v>
+      </c>
+      <c r="F16" t="n">
+        <v>20</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>research:defense.turret_t2</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>research.hint.defense.turret_t2</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>building.tier.value.turret</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>turret_light.t3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>turret_light</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>70</v>
+      </c>
+      <c r="F17" t="n">
+        <v>30</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>research:defense.turret_t3</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>research.hint.defense.turret_t3</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>building.tier.value.turret</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>turret_heavy.t1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>turret_heavy</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>building.tier.value.turret</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>turret_heavy.t2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>turret_heavy</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F19" t="n">
+        <v>30</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>research:defense.turret_t2</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>research.hint.defense.turret_t2</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>building.tier.value.turret</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>turret_heavy.t3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>turret_heavy</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>100</v>
+      </c>
+      <c r="F20" t="n">
+        <v>40</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>research:defense.turret_t3</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>research.hint.defense.turret_t3</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>building.tier.value.turret</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#BuildingTier-建筑等级.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingTier-建筑等级.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1318,6 +1318,92 @@
         <v>0</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>listening_post.t1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>listening_post</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>building.tier.value.listening_post</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>listening_post.t2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>listening_post</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>60</v>
+      </c>
+      <c r="F22" t="n">
+        <v>30</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>research:signal.listening_t2</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>research.hint.signal.listening_t2</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>building.tier.value.listening_post</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#BuildingTier-建筑等级.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingTier-建筑等级.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1404,6 +1404,135 @@
         <v>14</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>purifier.t1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>purifier</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>8</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>building.tier.value.purifier</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>purifier.t2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>purifier</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F24" t="n">
+        <v>30</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>research:environment.purifier_t2</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>research.hint.environment.purifier_t2</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>12</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>building.tier.value.purifier</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>purifier.t3</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>purifier</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>100</v>
+      </c>
+      <c r="F25" t="n">
+        <v>45</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>research:environment.purifier_t3</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>research.hint.environment.purifier_t3</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>16</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>building.tier.value.purifier</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#BuildingTier-建筑等级.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingTier-建筑等级.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1322,12 +1322,12 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>listening_post.t1</t>
+          <t>drop_station.t1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>listening_post</t>
+          <t>drop_station</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1350,11 +1350,11 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>building.tier.value.listening_post</t>
+          <t>building.tier.value.drop_station</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1365,55 +1365,55 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>listening_post.t2</t>
+          <t>drop_station.t2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>listening_post</t>
+          <t>drop_station</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F22" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>research:signal.listening_t2</t>
+          <t>research:expedition.drop_t2</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>research.hint.signal.listening_t2</t>
+          <t>research.hint.expedition.drop_t2</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>building.tier.value.listening_post</t>
+          <t>building.tier.value.drop_station</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>purifier.t1</t>
+          <t>listening_post.t1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>purifier</t>
+          <t>listening_post</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1436,27 +1436,27 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>building.tier.value.purifier</t>
+          <t>building.tier.value.listening_post</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>purifier.t2</t>
+          <t>listening_post.t2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>purifier</t>
+          <t>listening_post</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1470,66 +1470,152 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>research:environment.purifier_t2</t>
+          <t>research:signal.listening_t2</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>research.hint.environment.purifier_t2</t>
+          <t>research.hint.signal.listening_t2</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>building.tier.value.purifier</t>
+          <t>building.tier.value.listening_post</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
+          <t>purifier.t1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>purifier</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>grid.unlock.always</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>8</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>building.tier.value.purifier</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>purifier.t2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>purifier</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>60</v>
+      </c>
+      <c r="F26" t="n">
+        <v>30</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>research:environment.purifier_t2</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>research.hint.environment.purifier_t2</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>12</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>building.tier.value.purifier</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>purifier.t3</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>purifier</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D27" t="n">
         <v>3</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E27" t="n">
         <v>100</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F27" t="n">
         <v>45</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>research:environment.purifier_t3</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>research.hint.environment.purifier_t3</t>
         </is>
       </c>
-      <c r="I25" t="n">
+      <c r="I27" t="n">
         <v>16</v>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>building.tier.value.purifier</t>
         </is>
       </c>
-      <c r="K25" t="n">
+      <c r="K27" t="n">
         <v>24</v>
       </c>
     </row>
